--- a/backend/hospital_analysis_report.xlsx
+++ b/backend/hospital_analysis_report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:N23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,7 +456,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>icu_beds</t>
+          <t>icu_beds_used</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -466,15 +466,35 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>oxygen_supply</t>
+          <t>oxygen_used</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>medications_used</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>icu_bed_demand</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>oxygen_demand</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>medication_demand</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>last_renovation_year</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>operational_status</t>
         </is>
@@ -510,11 +530,27 @@
       <c r="G2" t="n">
         <v>5</v>
       </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="I2" t="n">
+        <v>300</v>
+      </c>
+      <c r="J2" t="n">
+        <v>15</v>
+      </c>
+      <c r="K2" t="n">
+        <v>20</v>
+      </c>
+      <c r="L2" t="n">
+        <v>350</v>
+      </c>
+      <c r="M2" t="n">
         <v>2018</v>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
@@ -550,11 +586,27 @@
       <c r="G3" t="n">
         <v>1</v>
       </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="I3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L3" t="n">
+        <v>120</v>
+      </c>
+      <c r="M3" t="n">
         <v>2015</v>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
@@ -590,11 +642,27 @@
       <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3</v>
+      </c>
+      <c r="L4" t="n">
+        <v>10</v>
+      </c>
+      <c r="M4" t="n">
         <v>2010</v>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Under Maintenance</t>
         </is>
@@ -630,11 +698,27 @@
       <c r="G5" t="n">
         <v>4</v>
       </c>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="I5" t="n">
+        <v>250</v>
+      </c>
+      <c r="J5" t="n">
+        <v>12</v>
+      </c>
+      <c r="K5" t="n">
+        <v>18</v>
+      </c>
+      <c r="L5" t="n">
+        <v>300</v>
+      </c>
+      <c r="M5" t="n">
         <v>2020</v>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
@@ -670,11 +754,27 @@
       <c r="G6" t="n">
         <v>1</v>
       </c>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="I6" t="n">
+        <v>90</v>
+      </c>
+      <c r="J6" t="n">
+        <v>4</v>
+      </c>
+      <c r="K6" t="n">
+        <v>6</v>
+      </c>
+      <c r="L6" t="n">
+        <v>100</v>
+      </c>
+      <c r="M6" t="n">
         <v>2016</v>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
@@ -710,11 +810,27 @@
       <c r="G7" t="n">
         <v>0</v>
       </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2</v>
+      </c>
+      <c r="L7" t="n">
+        <v>8</v>
+      </c>
+      <c r="M7" t="n">
         <v>2012</v>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
@@ -750,11 +866,27 @@
       <c r="G8" t="n">
         <v>3</v>
       </c>
-      <c r="H8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="I8" t="n">
+        <v>200</v>
+      </c>
+      <c r="J8" t="n">
+        <v>10</v>
+      </c>
+      <c r="K8" t="n">
+        <v>14</v>
+      </c>
+      <c r="L8" t="n">
+        <v>250</v>
+      </c>
+      <c r="M8" t="n">
         <v>2017</v>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
@@ -790,11 +922,27 @@
       <c r="G9" t="n">
         <v>1</v>
       </c>
-      <c r="H9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="I9" t="n">
+        <v>95</v>
+      </c>
+      <c r="J9" t="n">
+        <v>5</v>
+      </c>
+      <c r="K9" t="n">
+        <v>7</v>
+      </c>
+      <c r="L9" t="n">
+        <v>110</v>
+      </c>
+      <c r="M9" t="n">
         <v>2014</v>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
@@ -830,11 +978,27 @@
       <c r="G10" t="n">
         <v>0</v>
       </c>
-      <c r="H10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2</v>
+      </c>
+      <c r="L10" t="n">
+        <v>9</v>
+      </c>
+      <c r="M10" t="n">
         <v>2008</v>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Under Maintenance</t>
         </is>
@@ -870,11 +1034,27 @@
       <c r="G11" t="n">
         <v>4</v>
       </c>
-      <c r="H11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="I11" t="n">
+        <v>220</v>
+      </c>
+      <c r="J11" t="n">
+        <v>11</v>
+      </c>
+      <c r="K11" t="n">
+        <v>16</v>
+      </c>
+      <c r="L11" t="n">
+        <v>270</v>
+      </c>
+      <c r="M11" t="n">
         <v>2019</v>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
@@ -910,11 +1090,27 @@
       <c r="G12" t="n">
         <v>2</v>
       </c>
-      <c r="H12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="I12" t="n">
+        <v>120</v>
+      </c>
+      <c r="J12" t="n">
+        <v>6</v>
+      </c>
+      <c r="K12" t="n">
+        <v>9</v>
+      </c>
+      <c r="L12" t="n">
+        <v>140</v>
+      </c>
+      <c r="M12" t="n">
         <v>2013</v>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
@@ -950,11 +1146,587 @@
       <c r="G13" t="n">
         <v>0</v>
       </c>
-      <c r="H13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3</v>
+      </c>
+      <c r="L13" t="n">
+        <v>11</v>
+      </c>
+      <c r="M13" t="n">
         <v>2011</v>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>PMC General Hospital - Baner</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Pune</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>General Hospital</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>140</v>
+      </c>
+      <c r="F14" t="n">
+        <v>9</v>
+      </c>
+      <c r="G14" t="n">
+        <v>5</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>280</v>
+      </c>
+      <c r="J14" t="n">
+        <v>13</v>
+      </c>
+      <c r="K14" t="n">
+        <v>19</v>
+      </c>
+      <c r="L14" t="n">
+        <v>330</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2017</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>PMC Maternity Home - Aundh</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Pune</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Maternity Home</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>38</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>85</v>
+      </c>
+      <c r="J15" t="n">
+        <v>4</v>
+      </c>
+      <c r="K15" t="n">
+        <v>7</v>
+      </c>
+      <c r="L15" t="n">
+        <v>100</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2016</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>PMC Health Center - Shivaji Nagar</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Pune</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Health Center</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>19</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3</v>
+      </c>
+      <c r="L16" t="n">
+        <v>9</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2012</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Under Maintenance</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>PMC General Hospital - Vishrantwadi</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Pune</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>General Hospital</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>125</v>
+      </c>
+      <c r="F17" t="n">
+        <v>8</v>
+      </c>
+      <c r="G17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>230</v>
+      </c>
+      <c r="J17" t="n">
+        <v>11</v>
+      </c>
+      <c r="K17" t="n">
+        <v>15</v>
+      </c>
+      <c r="L17" t="n">
+        <v>290</v>
+      </c>
+      <c r="M17" t="n">
+        <v>2019</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>PMC Maternity Home - Camp</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Pune</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Maternity Home</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>32</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>98</v>
+      </c>
+      <c r="J18" t="n">
+        <v>5</v>
+      </c>
+      <c r="K18" t="n">
+        <v>7</v>
+      </c>
+      <c r="L18" t="n">
+        <v>115</v>
+      </c>
+      <c r="M18" t="n">
+        <v>2015</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>PMC Urban Health Center - Erandwane</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Pune</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Health Center</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>21</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2</v>
+      </c>
+      <c r="L19" t="n">
+        <v>10</v>
+      </c>
+      <c r="M19" t="n">
+        <v>2010</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>PMC General Hospital - Dhankawadi</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Pune</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>General Hospital</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>130</v>
+      </c>
+      <c r="F20" t="n">
+        <v>7</v>
+      </c>
+      <c r="G20" t="n">
+        <v>4</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>240</v>
+      </c>
+      <c r="J20" t="n">
+        <v>12</v>
+      </c>
+      <c r="K20" t="n">
+        <v>17</v>
+      </c>
+      <c r="L20" t="n">
+        <v>310</v>
+      </c>
+      <c r="M20" t="n">
+        <v>2021</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>PMC Maternity Home - Yerwada</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Pune</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Maternity Home</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>37</v>
+      </c>
+      <c r="F21" t="n">
+        <v>3</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>105</v>
+      </c>
+      <c r="J21" t="n">
+        <v>6</v>
+      </c>
+      <c r="K21" t="n">
+        <v>8</v>
+      </c>
+      <c r="L21" t="n">
+        <v>130</v>
+      </c>
+      <c r="M21" t="n">
+        <v>2014</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>PMC Urban Health Center - Kalyani Nagar</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Pune</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Health Center</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>23</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2</v>
+      </c>
+      <c r="L22" t="n">
+        <v>12</v>
+      </c>
+      <c r="M22" t="n">
+        <v>2011</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>PMC General Hospital - Hadapsar</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Pune</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>General Hospital</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>115</v>
+      </c>
+      <c r="F23" t="n">
+        <v>6</v>
+      </c>
+      <c r="G23" t="n">
+        <v>3</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>210</v>
+      </c>
+      <c r="J23" t="n">
+        <v>10</v>
+      </c>
+      <c r="K23" t="n">
+        <v>14</v>
+      </c>
+      <c r="L23" t="n">
+        <v>260</v>
+      </c>
+      <c r="M23" t="n">
+        <v>2018</v>
+      </c>
+      <c r="N23" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>

--- a/backend/hospital_analysis_report.xlsx
+++ b/backend/hospital_analysis_report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N23"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,7 +456,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>icu_beds_used</t>
+          <t>icu_beds</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -466,35 +466,15 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>oxygen_used</t>
+          <t>oxygen_supply</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>medications_used</t>
+          <t>last_renovation_year</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>icu_bed_demand</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>oxygen_demand</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>medication_demand</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>last_renovation_year</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>operational_status</t>
         </is>
@@ -530,27 +510,11 @@
       <c r="G2" t="n">
         <v>5</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>300</v>
-      </c>
-      <c r="J2" t="n">
-        <v>15</v>
-      </c>
-      <c r="K2" t="n">
-        <v>20</v>
-      </c>
-      <c r="L2" t="n">
-        <v>350</v>
-      </c>
-      <c r="M2" t="n">
         <v>2018</v>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
@@ -586,27 +550,11 @@
       <c r="G3" t="n">
         <v>1</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>100</v>
-      </c>
-      <c r="J3" t="n">
-        <v>5</v>
-      </c>
-      <c r="K3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L3" t="n">
-        <v>120</v>
-      </c>
-      <c r="M3" t="n">
         <v>2015</v>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
@@ -642,27 +590,11 @@
       <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L4" t="n">
-        <v>10</v>
-      </c>
-      <c r="M4" t="n">
         <v>2010</v>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Under Maintenance</t>
         </is>
@@ -698,27 +630,11 @@
       <c r="G5" t="n">
         <v>4</v>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>250</v>
-      </c>
-      <c r="J5" t="n">
-        <v>12</v>
-      </c>
-      <c r="K5" t="n">
-        <v>18</v>
-      </c>
-      <c r="L5" t="n">
-        <v>300</v>
-      </c>
-      <c r="M5" t="n">
         <v>2020</v>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
@@ -754,27 +670,11 @@
       <c r="G6" t="n">
         <v>1</v>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>90</v>
-      </c>
-      <c r="J6" t="n">
-        <v>4</v>
-      </c>
-      <c r="K6" t="n">
-        <v>6</v>
-      </c>
-      <c r="L6" t="n">
-        <v>100</v>
-      </c>
-      <c r="M6" t="n">
         <v>2016</v>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
@@ -810,27 +710,11 @@
       <c r="G7" t="n">
         <v>0</v>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>2</v>
-      </c>
-      <c r="L7" t="n">
-        <v>8</v>
-      </c>
-      <c r="M7" t="n">
         <v>2012</v>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
@@ -866,27 +750,11 @@
       <c r="G8" t="n">
         <v>3</v>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>200</v>
-      </c>
-      <c r="J8" t="n">
-        <v>10</v>
-      </c>
-      <c r="K8" t="n">
-        <v>14</v>
-      </c>
-      <c r="L8" t="n">
-        <v>250</v>
-      </c>
-      <c r="M8" t="n">
         <v>2017</v>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
@@ -922,27 +790,11 @@
       <c r="G9" t="n">
         <v>1</v>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>95</v>
-      </c>
-      <c r="J9" t="n">
-        <v>5</v>
-      </c>
-      <c r="K9" t="n">
-        <v>7</v>
-      </c>
-      <c r="L9" t="n">
-        <v>110</v>
-      </c>
-      <c r="M9" t="n">
         <v>2014</v>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
@@ -978,27 +830,11 @@
       <c r="G10" t="n">
         <v>0</v>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>2</v>
-      </c>
-      <c r="L10" t="n">
-        <v>9</v>
-      </c>
-      <c r="M10" t="n">
         <v>2008</v>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>Under Maintenance</t>
         </is>
@@ -1034,27 +870,11 @@
       <c r="G11" t="n">
         <v>4</v>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>220</v>
-      </c>
-      <c r="J11" t="n">
-        <v>11</v>
-      </c>
-      <c r="K11" t="n">
-        <v>16</v>
-      </c>
-      <c r="L11" t="n">
-        <v>270</v>
-      </c>
-      <c r="M11" t="n">
         <v>2019</v>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
@@ -1090,27 +910,11 @@
       <c r="G12" t="n">
         <v>2</v>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>120</v>
-      </c>
-      <c r="J12" t="n">
-        <v>6</v>
-      </c>
-      <c r="K12" t="n">
-        <v>9</v>
-      </c>
-      <c r="L12" t="n">
-        <v>140</v>
-      </c>
-      <c r="M12" t="n">
         <v>2013</v>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
@@ -1146,587 +950,11 @@
       <c r="G13" t="n">
         <v>0</v>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>3</v>
-      </c>
-      <c r="L13" t="n">
-        <v>11</v>
-      </c>
-      <c r="M13" t="n">
         <v>2011</v>
       </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>PMC General Hospital - Baner</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Pune</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>General Hospital</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Government</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>140</v>
-      </c>
-      <c r="F14" t="n">
-        <v>9</v>
-      </c>
-      <c r="G14" t="n">
-        <v>5</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>280</v>
-      </c>
-      <c r="J14" t="n">
-        <v>13</v>
-      </c>
-      <c r="K14" t="n">
-        <v>19</v>
-      </c>
-      <c r="L14" t="n">
-        <v>330</v>
-      </c>
-      <c r="M14" t="n">
-        <v>2017</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>PMC Maternity Home - Aundh</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Pune</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Maternity Home</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Private</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>38</v>
-      </c>
-      <c r="F15" t="n">
-        <v>2</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>85</v>
-      </c>
-      <c r="J15" t="n">
-        <v>4</v>
-      </c>
-      <c r="K15" t="n">
-        <v>7</v>
-      </c>
-      <c r="L15" t="n">
-        <v>100</v>
-      </c>
-      <c r="M15" t="n">
-        <v>2016</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>PMC Health Center - Shivaji Nagar</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Pune</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Health Center</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Government</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>19</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>3</v>
-      </c>
-      <c r="L16" t="n">
-        <v>9</v>
-      </c>
-      <c r="M16" t="n">
-        <v>2012</v>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>Under Maintenance</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>PMC General Hospital - Vishrantwadi</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Pune</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>General Hospital</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Government</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>125</v>
-      </c>
-      <c r="F17" t="n">
-        <v>8</v>
-      </c>
-      <c r="G17" t="n">
-        <v>4</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>230</v>
-      </c>
-      <c r="J17" t="n">
-        <v>11</v>
-      </c>
-      <c r="K17" t="n">
-        <v>15</v>
-      </c>
-      <c r="L17" t="n">
-        <v>290</v>
-      </c>
-      <c r="M17" t="n">
-        <v>2019</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>PMC Maternity Home - Camp</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Pune</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Maternity Home</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Government</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>32</v>
-      </c>
-      <c r="F18" t="n">
-        <v>2</v>
-      </c>
-      <c r="G18" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>98</v>
-      </c>
-      <c r="J18" t="n">
-        <v>5</v>
-      </c>
-      <c r="K18" t="n">
-        <v>7</v>
-      </c>
-      <c r="L18" t="n">
-        <v>115</v>
-      </c>
-      <c r="M18" t="n">
-        <v>2015</v>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>PMC Urban Health Center - Erandwane</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Pune</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Health Center</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Government</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>21</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>2</v>
-      </c>
-      <c r="L19" t="n">
-        <v>10</v>
-      </c>
-      <c r="M19" t="n">
-        <v>2010</v>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>PMC General Hospital - Dhankawadi</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Pune</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>General Hospital</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Private</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>130</v>
-      </c>
-      <c r="F20" t="n">
-        <v>7</v>
-      </c>
-      <c r="G20" t="n">
-        <v>4</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>240</v>
-      </c>
-      <c r="J20" t="n">
-        <v>12</v>
-      </c>
-      <c r="K20" t="n">
-        <v>17</v>
-      </c>
-      <c r="L20" t="n">
-        <v>310</v>
-      </c>
-      <c r="M20" t="n">
-        <v>2021</v>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>PMC Maternity Home - Yerwada</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Pune</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Maternity Home</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Private</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>37</v>
-      </c>
-      <c r="F21" t="n">
-        <v>3</v>
-      </c>
-      <c r="G21" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>105</v>
-      </c>
-      <c r="J21" t="n">
-        <v>6</v>
-      </c>
-      <c r="K21" t="n">
-        <v>8</v>
-      </c>
-      <c r="L21" t="n">
-        <v>130</v>
-      </c>
-      <c r="M21" t="n">
-        <v>2014</v>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>PMC Urban Health Center - Kalyani Nagar</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Pune</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Health Center</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Government</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>23</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" t="n">
-        <v>2</v>
-      </c>
-      <c r="L22" t="n">
-        <v>12</v>
-      </c>
-      <c r="M22" t="n">
-        <v>2011</v>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>PMC General Hospital - Hadapsar</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Pune</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>General Hospital</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Government</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>115</v>
-      </c>
-      <c r="F23" t="n">
-        <v>6</v>
-      </c>
-      <c r="G23" t="n">
-        <v>3</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>210</v>
-      </c>
-      <c r="J23" t="n">
-        <v>10</v>
-      </c>
-      <c r="K23" t="n">
-        <v>14</v>
-      </c>
-      <c r="L23" t="n">
-        <v>260</v>
-      </c>
-      <c r="M23" t="n">
-        <v>2018</v>
-      </c>
-      <c r="N23" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
